--- a/stories/arbres/ATOM-REL.MOQ.002-05.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.002-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aurélien est au parc. Maman est sur le banc. Léo est à l'écart. Il est près du buisson. Ses épaules sont basses. Un enfant a ri un tout petit moment, puis il est parti. Aurélien se souvient. On peut rejoindre. Rejoindre, c'est aller vers lui. Aurélien marche vers Léo. Il dit : tu veux jouer ? Inviter, c'est demander. Léo dit : d'accord. Ils roulent les billes. Plus tard, près des jeux d'eau, Léo est encore à l'écart. Ça continue un peu. Aurélien va vers maman. Maman est l'adulte. Aurélien dit : ça continue. On prévient un adulte si ça continue. Maman s'approche. Elle reste près d'eux. Ils font un château de sable. Le soir, Aurélien raconte à papa. Papa dit : tu as su rejoindre. Tu as su inviter. Tu as prévenu un adulte.</t>
+          <t>Aurélien est au parc. Maman est sur le banc. Léo est à l'écart. Il est près du buisson. Ses épaules sont basses. Un enfant a ri un tout petit moment, puis il est parti. Aurélien se souvient. On peut rejoindre. Rejoindre, c'est aller vers lui. Aurélien marche vers Léo. Tu veux jouer ? Inviter, c'est demander. D'accord. Ils roulent les billes. Plus tard, près des jeux d'eau, Léo est encore à l'écart. Ça continue un peu. Aurélien va vers maman. Maman est l'adulte. Ça continue. On prévient un adulte si ça continue. Maman s'approche. Elle reste près d'eux. Ils font un château de sable. Le soir, Aurélien raconte à papa. Tu as su rejoindre. Tu as su inviter. Tu as prévenu un adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aurélien est au parc. Maman est sur le banc. Léo est à l'écart. Il est près du buisson. Ses épaules sont basses. Un enfant a ri un tout petit moment, puis il est parti. Aurélien se souvient. On peut rejoindre. Rejoindre, c'est aller vers lui. Aurélien marche vers Léo.
+narrateur|Tu veux jouer ? Inviter, c'est demander.
+copain|D'accord. Ils roulent les billes. Plus tard, près des jeux d'eau, Léo est encore à l'écart. Ça continue un peu.
+narrateur|Aurélien va vers maman. Maman est l'adulte.
+enfant-m|Ça continue. On prévient un adulte si ça continue. Maman s'approche. Elle reste près d'eux. Ils font un château de sable.
+narrateur|Le soir, Aurélien raconte à papa.
+papa|Tu as su rejoindre. Tu as su inviter. Tu as prévenu un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Léo est à l'écart. Que fait Aurélien ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Aurélien a su rejoindre Léo. Il a pu inviter. Il a prévenu un adulte, car ça continue. Papa et maman ont écouté.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Aurélien secoue le sable. Maman lui tend le manteau.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.002-05.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.002-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,11 @@
 papa|Tu as su rejoindre. Tu as su inviter. Tu as prévenu un adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1509,7 @@
           <t>narrateur|Léo est à l'écart. Que fait Aurélien ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1681,7 @@
           <t>narrateur|Aurélien a su rejoindre Léo. Il a pu inviter. Il a prévenu un adulte, car ça continue. Papa et maman ont écouté.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1845,7 @@
           <t>narrateur|Aurélien secoue le sable. Maman lui tend le manteau.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.MOQ.002-05.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.002-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Aurélien rejoint Léo au parc</t>
+          <t>Raphaël rejoint Amir au parc</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>REL.MOQ.003</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une pomme de pin roule sous le banc. Raphaël voit Amir près du buisson. Il le rejoint, l'invite aux billes. Près des jeux d'eau, ça continue. Il prévient maman. Le soir, il raconte à papa.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aurélien est au parc. Maman est sur le banc. Léo est à l'écart. Il est près du buisson. Ses épaules sont basses. Un enfant a ri un tout petit moment, puis il est parti. Aurélien se souvient. On peut rejoindre. Rejoindre, c'est aller vers lui. Aurélien marche vers Léo. Tu veux jouer ? Inviter, c'est demander. D'accord. Ils roulent les billes. Plus tard, près des jeux d'eau, Léo est encore à l'écart. Ça continue un peu. Aurélien va vers maman. Maman est l'adulte. Ça continue. On prévient un adulte si ça continue. Maman s'approche. Elle reste près d'eux. Ils font un château de sable. Le soir, Aurélien raconte à papa. Tu as su rejoindre. Tu as su inviter. Tu as prévenu un adulte.</t>
+          <t>Sous le banc du parc, une pomme de pin roule. Elle fait un bruit sec, tout petit. La fontaine chuchote, tout près. L'eau brille, puis retombe. Du sable s'est glissé dans une chaussette. Il gratte, un peu. Le panier de maman sent le thermos. Le banc est chaud, Raphaël. Tu ôtes le sable de ta chaussette ? Oui, maman. Raphaël secoue la chaussette. Le sable tombe, tout fin. Je reste ici, sur le banc. Tu vas vers le bac ? Oui. En ce moment, Raphaël est au parc. Les billes cliquettent, dans une boîte. Amir est à l'écart. Il est près du buisson. Ses épaules sont basses. Il tient une bille verte, sans la rouler. Un enfant a ri un tout petit moment, puis il est parti. Raphaël se souvient. On peut rejoindre. Rejoindre, c'est aller vers lui. Raphaël marche vers Amir. L'herbe est sèche, elle craque. Tu veux jouer ? Inviter, c'est demander. Amir dit d'accord. Ils roulent les billes. La bille verte fait un petit chemin. Elle est lisse et froide. Je vous vois, du banc. Les billes roulent bien. Plus tard, près des jeux d'eau. L'eau tapote les dalles. Ça sent le savon de la fontaine, un peu. Amir est encore à l'écart. Ça continue un peu. Raphaël va vers maman. Maman est l'adulte, sur le banc. Ça continue. On prévient un adulte, si ça continue. Je t'écoute, Raphaël. Je m'approche. Maman reste près d'eux. Ils font un château de sable. Le sable est frais, près de l'eau. Il coule entre les doigts. Bravo, Raphaël. Tu as rejoint Amir. Tu l'as invité. Tu m'as prévenue, car ça continue. C'est du bon travail. Le château a une petite porte ? Oui. Amir la creuse. Vous creusez ensemble. Le soir, Raphaël raconte à papa. Le thermos est vide, sur la table. Amir était à l'écart. Je l'ai rejoint. Je l'ai invité. Ça continuait. J'ai prévenu maman. Tu as su rejoindre. Tu as su inviter. Tu as prévenu un adulte. Bravo, Raphaël. Tu as fait du bon travail. Tu as encore du sable, dans la chaussette ? Un peu. On la secoue, encore une fois. La pomme de pin reste sous le banc, au parc.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,13 +1329,81 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aurélien est au parc. Maman est sur le banc. Léo est à l'écart. Il est près du buisson. Ses épaules sont basses. Un enfant a ri un tout petit moment, puis il est parti. Aurélien se souvient. On peut rejoindre. Rejoindre, c'est aller vers lui. Aurélien marche vers Léo.
-narrateur|Tu veux jouer ? Inviter, c'est demander.
-copain|D'accord. Ils roulent les billes. Plus tard, près des jeux d'eau, Léo est encore à l'écart. Ça continue un peu.
-narrateur|Aurélien va vers maman. Maman est l'adulte.
-enfant-m|Ça continue. On prévient un adulte si ça continue. Maman s'approche. Elle reste près d'eux. Ils font un château de sable.
-narrateur|Le soir, Aurélien raconte à papa.
-papa|Tu as su rejoindre. Tu as su inviter. Tu as prévenu un adulte.</t>
+          <t>narrateur|Sous le banc du parc, une pomme de pin roule.
+narrateur|Elle fait un bruit sec, tout petit.
+narrateur|La fontaine chuchote, tout près.
+narrateur|L'eau brille, puis retombe.
+narrateur|Du sable s'est glissé dans une chaussette.
+narrateur|Il gratte, un peu.
+narrateur|Le panier de maman sent le thermos.
+maman|Le banc est chaud, Raphaël.
+maman|Tu ôtes le sable de ta chaussette ?
+enfant-m|Oui, maman.
+narrateur|Raphaël secoue la chaussette.
+narrateur|Le sable tombe, tout fin.
+maman|Je reste ici, sur le banc.
+maman|Tu vas vers le bac ?
+enfant-m|Oui.
+narrateur|En ce moment, Raphaël est au parc.
+narrateur|Les billes cliquettent, dans une boîte.
+narrateur|Amir est à l'écart.
+narrateur|Il est près du buisson.
+narrateur|Ses épaules sont basses.
+narrateur|Il tient une bille verte, sans la rouler.
+narrateur|Un enfant a ri un tout petit moment, puis il est parti.
+narrateur|Raphaël se souvient.
+narrateur|On peut rejoindre.
+narrateur|Rejoindre, c'est aller vers lui.
+narrateur|Raphaël marche vers Amir.
+narrateur|L'herbe est sèche, elle craque.
+enfant-m|Tu veux jouer ?
+narrateur|Inviter, c'est demander.
+narrateur|Amir dit d'accord.
+narrateur|Ils roulent les billes.
+narrateur|La bille verte fait un petit chemin.
+narrateur|Elle est lisse et froide.
+maman|Je vous vois, du banc.
+maman|Les billes roulent bien.
+narrateur|Plus tard, près des jeux d'eau.
+narrateur|L'eau tapote les dalles.
+narrateur|Ça sent le savon de la fontaine, un peu.
+narrateur|Amir est encore à l'écart.
+narrateur|Ça continue un peu.
+narrateur|Raphaël va vers maman.
+narrateur|Maman est l'adulte, sur le banc.
+enfant-m|Ça continue.
+enfant-m|On prévient un adulte, si ça continue.
+maman|Je t'écoute, Raphaël.
+maman|Je m'approche.
+narrateur|Maman reste près d'eux.
+narrateur|Ils font un château de sable.
+narrateur|Le sable est frais, près de l'eau.
+narrateur|Il coule entre les doigts.
+maman|Bravo, Raphaël.
+maman|Tu as rejoint Amir.
+maman|Tu l'as invité.
+maman|Tu m'as prévenue, car ça continue.
+maman|C'est du bon travail.
+maman|Le château a une petite porte ?
+enfant-m|Oui.
+enfant-m|Amir la creuse.
+maman|Vous creusez ensemble.
+narrateur|Le soir, Raphaël raconte à papa.
+narrateur|Le thermos est vide, sur la table.
+enfant-m|Amir était à l'écart.
+enfant-m|Je l'ai rejoint.
+enfant-m|Je l'ai invité.
+enfant-m|Ça continuait.
+enfant-m|J'ai prévenu maman.
+papa|Tu as su rejoindre.
+papa|Tu as su inviter.
+papa|Tu as prévenu un adulte.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+papa|Tu as encore du sable, dans la chaussette ?
+enfant-m|Un peu.
+papa|On la secoue, encore une fois.
+narrateur|La pomme de pin reste sous le banc, au parc.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1350,7 +1435,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Léo est à l'écart. Que fait Aurélien ?</t>
+          <t>Amir est à l'écart. Que fait Raphaël ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1506,7 +1591,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Léo est à l'écart. Que fait Aurélien ?</t>
+          <t>narrateur|Amir est à l'écart.
+narrateur|Que fait Raphaël ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1534,7 +1620,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Aurélien a su rejoindre Léo. Il a pu inviter. Il a prévenu un adulte, car ça continue. Papa et maman ont écouté.</t>
+          <t>Raphaël a su rejoindre Amir. Il a pu inviter. Il a prévenu un adulte, car ça continue. Maman et moi, on t'écoute. Bravo. C'est du bon travail. J'ai rejoint. J'ai invité. Oui. Et un adulte, si ça continue.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1678,7 +1764,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Aurélien a su rejoindre Léo. Il a pu inviter. Il a prévenu un adulte, car ça continue. Papa et maman ont écouté.</t>
+          <t>narrateur|Raphaël a su rejoindre Amir.
+narrateur|Il a pu inviter.
+narrateur|Il a prévenu un adulte, car ça continue.
+papa|Maman et moi, on t'écoute.
+papa|Bravo.
+maman|C'est du bon travail.
+enfant-m|J'ai rejoint.
+enfant-m|J'ai invité.
+maman|Oui.
+papa|Et un adulte, si ça continue.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1706,7 +1801,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Aurélien secoue le sable. Maman lui tend le manteau.</t>
+          <t>Raphaël secoue le sable. Le manteau, maintenant ? Oui, maman. Maman lui tend le manteau. Il sent encore le parc. La fontaine chuchotait, tu t'en souviens ? Oui. Et la bille verte. Amir l'a fait rouler, avec toi. Le thermos sonne, vide, dans le panier.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1937,16 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Aurélien secoue le sable. Maman lui tend le manteau.</t>
+          <t>narrateur|Raphaël secoue le sable.
+maman|Le manteau, maintenant ?
+enfant-m|Oui, maman.
+narrateur|Maman lui tend le manteau.
+maman|Il sent encore le parc.
+papa|La fontaine chuchotait, tu t'en souviens ?
+enfant-m|Oui.
+enfant-m|Et la bille verte.
+papa|Amir l'a fait rouler, avec toi.
+narrateur|Le thermos sonne, vide, dans le panier.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1974,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai rejoint Amir. J'ai raconté à papa. Bravo. Tu as fait du bon travail. Une pomme de pin a roulé, tout le jour. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2114,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai rejoint Amir.
+enfant-m|J'ai raconté à papa.
+papa|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Une pomme de pin a roulé, tout le jour.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2179,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.002-05.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.002-05.xlsx
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sous le banc du parc, une pomme de pin roule. Elle fait un bruit sec, tout petit. La fontaine chuchote, tout près. L'eau brille, puis retombe. Du sable s'est glissé dans une chaussette. Il gratte, un peu. Le panier de maman sent le thermos. Le banc est chaud, Raphaël. Tu ôtes le sable de ta chaussette ? Oui, maman. Raphaël secoue la chaussette. Le sable tombe, tout fin. Je reste ici, sur le banc. Tu vas vers le bac ? Oui. En ce moment, Raphaël est au parc. Les billes cliquettent, dans une boîte. Amir est à l'écart. Il est près du buisson. Ses épaules sont basses. Il tient une bille verte, sans la rouler. Un enfant a ri un tout petit moment, puis il est parti. Raphaël se souvient. On peut rejoindre. Rejoindre, c'est aller vers lui. Raphaël marche vers Amir. L'herbe est sèche, elle craque. Tu veux jouer ? Inviter, c'est demander. Amir dit d'accord. Ils roulent les billes. La bille verte fait un petit chemin. Elle est lisse et froide. Je vous vois, du banc. Les billes roulent bien. Plus tard, près des jeux d'eau. L'eau tapote les dalles. Ça sent le savon de la fontaine, un peu. Amir est encore à l'écart. Ça continue un peu. Raphaël va vers maman. Maman est l'adulte, sur le banc. Ça continue. On prévient un adulte, si ça continue. Je t'écoute, Raphaël. Je m'approche. Maman reste près d'eux. Ils font un château de sable. Le sable est frais, près de l'eau. Il coule entre les doigts. Bravo, Raphaël. Tu as rejoint Amir. Tu l'as invité. Tu m'as prévenue, car ça continue. C'est du bon travail. Le château a une petite porte ? Oui. Amir la creuse. Vous creusez ensemble. Le soir, Raphaël raconte à papa. Le thermos est vide, sur la table. Amir était à l'écart. Je l'ai rejoint. Je l'ai invité. Ça continuait. J'ai prévenu maman. Tu as su rejoindre. Tu as su inviter. Tu as prévenu un adulte. Bravo, Raphaël. Tu as fait du bon travail. Tu as encore du sable, dans la chaussette ? Un peu. On la secoue, encore une fois. La pomme de pin reste sous le banc, au parc.</t>
+          <t>Sous le banc du parc, une pomme de pin roule. Elle fait un bruit sec, tout petit. La fontaine chuchote, tout près. L'eau brille, puis retombe. Du sable s'est glissé dans une chaussette. Il gratte, un peu. Le panier de maman sent le thermos. Le banc est chaud, Raphaël. Tu ôtes le sable de ta chaussette ? Oui, maman. Raphaël secoue la chaussette. Le sable tombe, tout fin. Je reste ici, sur le banc. Tu vas vers le bac ? Oui. En ce moment, Raphaël est au parc. Les billes cliquettent, dans une boîte. Amir est à l'écart. Il est près du buisson. Ses épaules sont basses. Il tient une bille verte, sans la rouler. Un enfant a ri un tout petit moment, puis il est parti. Raphaël se souvient. On peut rejoindre. Rejoindre, c'est aller vers lui. Raphaël marche vers Amir. L'herbe est sèche, elle craque. Tu veux jouer ? Inviter, c'est demander. Amir dit d'accord. Ils roulent les billes. La bille verte fait un petit chemin. Elle est lisse et froide. Je vous vois, du banc. Les billes roulent bien. Plus tard, près des jeux d'eau. L'eau tapote les dalles. Ça sent le savon de la fontaine, un peu. Amir est encore à l'écart. Ça continue un peu. Raphaël va vers maman. Maman est l'adulte, sur le banc. Ça continue. On prévient un adulte, si ça continue. Je t'écoute, Raphaël. Je m'approche. Maman reste près d'eux. Ils font un château de sable. Le sable est frais, près de l'eau. Il coule entre les doigts. Bravo, Raphaël. Tu as rejoint Amir. Tu l'as invité. Tu m'as prévenue, car ça continue. Le château a une petite porte ? Oui. Amir la creuse. Vous creusez ensemble. Le soir, Raphaël raconte à papa. Le thermos est vide, sur la table. Amir était à l'écart. Je l'ai rejoint. Je l'ai invité. Ça continuait. J'ai prévenu maman. Tu as su rejoindre. Tu as su inviter. Tu as prévenu un adulte. Bravo, Raphaël. Tu as encore du sable, dans la chaussette ? Un peu. On la secoue, encore une fois. La pomme de pin reste sous le banc, au parc.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aurélien est au parc. Maman est sur le banc. Léo est à l'écart. Il est près du buisson. Ses épaules sont basses. Un enfant a ri un tout petit moment, puis il est parti. Aurélien se souvient. On peut &lt;emphasis level="moderate"&gt;rejoindre&lt;/emphasis&gt;. Rejoindre, c'est aller vers lui. Aurélien marche vers Léo. Il dit : tu veux jouer ? Inviter, c'est demander. Léo dit : d'accord. Ils roulent les billes. Plus tard, près des jeux d'eau, Léo est encore à l'écart. Ça continue un peu. Aurélien va vers maman. Maman est l'adulte. Aurélien dit : ça continue. On prévient un adulte si ça continue. Maman s'approche. Elle reste près d'eux. Ils font un château de sable. Le soir, Aurélien raconte à papa. Papa dit : tu as su rejoindre. Tu as su inviter. Tu as prévenu un adulte.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sous le banc du parc, une pomme de pin roule. Elle fait un bruit sec, tout petit. La fontaine chuchote, tout près. L'eau brille, puis retombe. Du sable s'est glissé dans une chaussette. Il gratte, un peu. Le panier de maman sent le thermos. Le banc est chaud, Raphaël. Tu ôtes le sable de ta chaussette ? Oui, maman. Raphaël secoue la chaussette. Le sable tombe, tout fin. Je reste ici, sur le banc. Tu vas vers le bac ? Oui. En ce moment, Raphaël est au parc. Les billes cliquettent, dans une boîte. Amir est à l'écart. Il est près du buisson. Ses épaules sont basses. Il tient une bille verte, sans la rouler. Un enfant a ri un tout petit moment, puis il est parti. Raphaël se souvient. On peut rejoindre. Rejoindre, c'est aller vers lui. Raphaël marche vers Amir. L'herbe est sèche, elle craque. Tu veux jouer ? Inviter, c'est demander. Amir dit d'accord. Ils roulent les billes. La bille verte fait un petit chemin. Elle est lisse et froide. Je vous vois, du banc. Les billes roulent bien. Plus tard, près des jeux d'eau. L'eau tapote les dalles. Ça sent le savon de la fontaine, un peu. Amir est encore à l'écart. Ça continue un peu. Raphaël va vers maman. Maman est l'adulte, sur le banc. Ça continue. On prévient un adulte, si ça continue. Je t'écoute, Raphaël. Je m'approche. Maman reste près d'eux. Ils font un château de sable. Le sable est frais, près de l'eau. Il coule entre les doigts. Bravo, Raphaël. Tu as rejoint Amir. Tu l'as invité. Tu m'as prévenue, car ça continue. Le château a une petite porte ? Oui. Amir la creuse. Vous creusez ensemble. Le soir, Raphaël raconte à papa. Le thermos est vide, sur la table. Amir était à l'écart. Je l'ai rejoint. Je l'ai invité. Ça continuait. J'ai prévenu maman. Tu as su rejoindre. Tu as su inviter. Tu as prévenu un adulte. Bravo, Raphaël. Tu as encore du sable, dans la chaussette ? Un peu. On la secoue, encore une fois. La pomme de pin reste sous le banc, au parc.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1383,7 +1383,6 @@
 maman|Tu as rejoint Amir.
 maman|Tu l'as invité.
 maman|Tu m'as prévenue, car ça continue.
-maman|C'est du bon travail.
 maman|Le château a une petite porte ?
 enfant-m|Oui.
 enfant-m|Amir la creuse.
@@ -1399,7 +1398,6 @@
 papa|Tu as su inviter.
 papa|Tu as prévenu un adulte.
 papa|Bravo, Raphaël.
-papa|Tu as fait du bon travail.
 papa|Tu as encore du sable, dans la chaussette ?
 enfant-m|Un peu.
 papa|On la secoue, encore une fois.
@@ -1440,7 +1438,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Léo est à l'écart. Que fait Aurélien ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir est à l'écart. Que fait Raphaël ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1595,7 +1593,6 @@
 narrateur|Que fait Raphaël ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1620,12 +1617,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a su rejoindre Amir. Il a pu inviter. Il a prévenu un adulte, car ça continue. Maman et moi, on t'écoute. Bravo. C'est du bon travail. J'ai rejoint. J'ai invité. Oui. Et un adulte, si ça continue.</t>
+          <t>Raphaël a su rejoindre Amir. Il a pu inviter. Il a prévenu un adulte, car ça continue. Maman et moi, on t'écoute. Bravo. J'ai rejoint. J'ai invité. Oui. Et un adulte, si ça continue.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aurélien a su &lt;emphasis level="moderate"&gt;rejoindre&lt;/emphasis&gt; Léo. Il a pu inviter. Il a prévenu un adulte, car ça continue. Papa et maman ont écouté.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël a su rejoindre Amir. Il a pu inviter. Il a prévenu un adulte, car ça continue. Maman et moi, on t'écoute. Bravo. J'ai rejoint. J'ai invité. Oui. Et un adulte, si ça continue.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1769,14 +1766,12 @@
 narrateur|Il a prévenu un adulte, car ça continue.
 papa|Maman et moi, on t'écoute.
 papa|Bravo.
-maman|C'est du bon travail.
 enfant-m|J'ai rejoint.
 enfant-m|J'ai invité.
 maman|Oui.
 papa|Et un adulte, si ça continue.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1806,7 +1801,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Aurélien secoue le sable. Maman lui tend le manteau.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël secoue le sable. Le manteau, maintenant ? Oui, maman. Maman lui tend le manteau. Il sent encore le parc. La fontaine chuchotait, tu t'en souviens ? Oui. Et la bille verte. Amir l'a fait rouler, avec toi. Le thermos sonne, vide, dans le panier.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1949,7 +1944,6 @@
 narrateur|Le thermos sonne, vide, dans le panier.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1974,12 +1968,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai rejoint Amir. J'ai raconté à papa. Bravo. Tu as fait du bon travail. Une pomme de pin a roulé, tout le jour. L'histoire est finie.</t>
+          <t>J'ai rejoint Amir. J'ai raconté à papa. Bravo. Une pomme de pin a roulé, tout le jour.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai rejoint Amir. J'ai raconté à papa. Bravo. Une pomme de pin a roulé, tout le jour.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2117,12 +2111,9 @@
           <t>enfant-m|J'ai rejoint Amir.
 enfant-m|J'ai raconté à papa.
 papa|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Une pomme de pin a roulé, tout le jour.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Une pomme de pin a roulé, tout le jour.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2141,7 +2132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2186,6 +2177,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.002-05.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.002-05.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Aurélien, Léo, maman, papa</t>
+          <t>Raphaël, Amir, maman, papa</t>
         </is>
       </c>
     </row>
